--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260817.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260817.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>918,044,000</t>
+          <t>913,037,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.59%</t>
+          <t>9.54%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>178,214,000</t>
+          <t>177,211,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>9.41%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>39,027,000</t>
+          <t>38,830,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.17%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>371,139,486</t>
+          <t>370,440,486</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.98%</t>
+          <t>5.79%</t>
         </is>
       </c>
     </row>
@@ -699,56 +699,56 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>109,474,000</t>
+          <t>109,122,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>4.02%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>608,249,270</t>
+          <t>187,201,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>188,260,000</t>
+          <t>602,716,270</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.56%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,084,000</t>
+          <t>5,062,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -787,56 +787,56 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>27,298,000</t>
+          <t>27,239,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,114</t>
+          <t>456,296,250</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>465,231,250</t>
+          <t>64,392,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -853,122 +853,122 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>366,839,964</t>
+          <t>360,120,964</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>64,840,000</t>
+          <t>131,951,945</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>132,969,945</t>
+          <t>26,219,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>26,367,000</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>83,490,000</t>
+          <t>98,298,442</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>83,020,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -985,78 +985,78 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>230,616,516</t>
+          <t>227,363,516</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>98,854,442</t>
+          <t>199,761,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>202,817,000</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>145,652,000</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -1073,34 +1073,34 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>29,028,000</t>
+          <t>28,901,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>131,978,000</t>
+          <t>99,033,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1117,56 +1117,56 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>35,720,000</t>
+          <t>35,510,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>99,617,000</t>
+          <t>188,603,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>189,910,000</t>
+          <t>1,274</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -1183,56 +1183,56 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>55,187,000</t>
+          <t>54,488,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>259,999,845</t>
+          <t>272,189,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>273,066,000</t>
+          <t>257,999,845</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,253,000</t>
+          <t>13,761,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>92,615,061</t>
+          <t>91,230,061</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,437,150,124</t>
+          <t>22,762,660,056</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,978,818,559</t>
+          <t>5,003,111,202</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-56,886,455</t>
+          <t>-404,917,552</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
